--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260826.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260826.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>132,235</t>
+          <t>132,835</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.40%</t>
+          <t>26.14%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>15,025</t>
+          <t>15,125</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.80%</t>
+          <t>7.98%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>95,930</t>
+          <t>96,380</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.78%</t>
+          <t>7.94%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>48,765</t>
+          <t>48,975</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.57%</t>
+          <t>6.65%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>116,395</t>
+          <t>116,895</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.45%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>57,140</t>
+          <t>57,390</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5,435</t>
+          <t>5,535</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>62,885</t>
+          <t>63,155</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>19,015</t>
+          <t>19,115</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>43,365</t>
+          <t>43,555</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>17,613</t>
+          <t>17,713</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>73,795</t>
+          <t>74,115</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>19,465</t>
+          <t>19,565</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>30,330</t>
+          <t>30,460</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>49,045</t>
+          <t>49,255</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>25,498</t>
+          <t>25,608</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>34,770</t>
+          <t>34,920</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>18,720</t>
+          <t>18,820</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>56,898</t>
+          <t>57,138</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1034,95 +1034,95 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>121,715</t>
+          <t>75,413,159</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>20,438</t>
+          <t>7,690</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7,690</t>
+          <t>122,235</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>69,368,405</t>
+          <t>20,538</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1161,56 +1161,56 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>17,645</t>
+          <t>17,745</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,767</t>
+          <t>15,371</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,271</t>
+          <t>18,867</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>41,490</t>
+          <t>41,670</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>35,980</t>
+          <t>36,130</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>486,007</t>
+          <t>611,255</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>125,249</t>
+          <t>108,914</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
